--- a/Documentacion/VersionesDiagramaDeGantt/GanttNexoUD_SprintFinal_V2.xlsx
+++ b/Documentacion/VersionesDiagramaDeGantt/GanttNexoUD_SprintFinal_V2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tomas\Documents\NEXO-UD\Documentacion\VersionesDiagramaDeGantt\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5F45D3-B07F-43C2-9C5B-2B53C61EE7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BCBC8F-7B92-4082-8EB0-F89CB2A427A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1670,8 +1670,8 @@
       <c r="F22" s="32"/>
       <c r="G22" s="32"/>
       <c r="H22" s="32"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
       <c r="K22" s="32"/>
       <c r="L22" s="32"/>
     </row>
